--- a/VegSP_lista.xlsx
+++ b/VegSP_lista.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -199,6 +199,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -648,7 +651,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Quintal Vegano</t>
+          <t>VHMOR Bistrô</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -658,268 +661,876 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Brasileira contemporânea</t>
+          <t>Brasileira / Lanches</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Pinheiros / SP</t>
+          <t>República / SP</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Rua Example, 100</t>
+          <t>Av. São Luís, 187 - Subsolo 1, Lojas 22/23</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Ter a Dom</t>
+          <t>Seg a Sex (+ 2 sáb/mês)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/quintalvegano</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>instagram.com/vhmorbistro</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2 sábados/mês anunciados no Instagram</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Raízes Mercado</t>
+          <t>Salad Days</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Orgânicos e naturais</t>
+          <t>Hambúrguer / Feijoada</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Paraíso / SP</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Rua Arujá, 57</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Qua, Sáb: 12-15h e 17-22h; Qui e Sex: 17-22h</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/saladdays.sp</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Feijoada aos sábados</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Rato Rosa</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>República / SP</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Rua Rego Freitas, 311</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/ratorosapizzaria</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Fermentação natural; fecha último dom do mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>POP Comida Vegana</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira / Pizza</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Rua Fernando de Albuquerque, 142/144</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/popvegano</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Buffet à vontade no almoço; rodízio de pizza à noite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Hera Veggie</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Pães / Lanches</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Rua Fernando de Albuquerque, 93</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Sáb (pizza sáb 18-21h)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/heraveggie</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Pizza aos sábados das 18h às 21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>It's Vegan</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Lanches / Brunch</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Rua Fernando de Albuquerque, 89</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/itsvegan.sp</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Brunch aos domingos; fecha mais tarde sex e sáb (23h30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Jaffa SP</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Israelense / Árabe</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Santa Cecília / SP</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Rua Fortunato, 251</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/jaffasp</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Falafel premiado; almoço 12-14h30 e jantar 18-22h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pratada SP</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Vila Buarque / SP</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Rua General Jardim, 160</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/pratada.sp</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Sáb e Dom: 12h às 15h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Congolinária</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Africana (Congolesa)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Sumaré / SP</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Av. Professor Alfonso Bovero, 382</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/congolinaria</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Dom fecha às 21h; 2ª unidade: Rua Caquito, 251 - Penha</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Congolinária Penha</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Africana (Congolesa)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Penha / SP</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Rua Caquito, 251</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/congolinaria</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Dom fecha às 21h</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Vegano SP</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira contemporânea</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Alameda Ministro Rocha Azevedo, 760</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/veganosp</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Sáb e Dom: 11h30 às 16h</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Bobó Empório Vegano</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira / Buffet</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Jardim Paulista / SP</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Alameda Campinas, 1060</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/boboemporio</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Buffet livre seg a sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>A Coruja Churrascaria Vegana</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Churrasco</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Lapa / SP</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Rua Tito, 25</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/acorujavegana</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Primeira churrascaria vegana de SP; rodízio disponível</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Sushimar</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Japonesa</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Alameda Campinas, 1287</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/sushimarvegano</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Almoço ter-sex 12-14h30; jantar ter-sáb 19-22h30; sáb-dom-fer 12-16h</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Casa Raw</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Vegana criativa / Sem glúten</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Perdizes / SP</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Rua Doutor Franco da Rocha, 515</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/casaraw</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Jardim charmoso; vinhos naturais; dom fecha às 16h30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Tau Cozinha</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Contemporânea / Franco-japonesa</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>Vila Madalena / SP</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Rua Example, 200</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Seg a Sáb</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>raizesmercado.com.br</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Rua Harmonia, 797</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/taucozinhaveg</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Almoço sáb 12-15h e dom 12h30-16h</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Loving Hut</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Asiática / Variada</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Vila Mariana / SP</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Rua França Pinto, 243</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/lovinghutsp</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Rede internacional; cardápio extenso</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="n"/>
@@ -3080,6 +3691,1206 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="n"/>
       <c r="J200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+      <c r="J201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
+      <c r="J202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+      <c r="J203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
+      <c r="J204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+      <c r="J205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
+      <c r="J206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
+      <c r="J207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+      <c r="J208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+      <c r="J209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="5" t="n"/>
+      <c r="J210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
+      <c r="J211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+      <c r="J212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
+      <c r="J213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
+      <c r="J214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="5" t="n"/>
+      <c r="I215" s="5" t="n"/>
+      <c r="J215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="5" t="n"/>
+      <c r="I216" s="5" t="n"/>
+      <c r="J216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
+      <c r="I217" s="5" t="n"/>
+      <c r="J217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="5" t="n"/>
+      <c r="I218" s="5" t="n"/>
+      <c r="J218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
+      <c r="J219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="5" t="n"/>
+      <c r="I220" s="5" t="n"/>
+      <c r="J220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
+      <c r="J221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
+      <c r="J222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="5" t="n"/>
+      <c r="I223" s="5" t="n"/>
+      <c r="J223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="5" t="n"/>
+      <c r="I224" s="5" t="n"/>
+      <c r="J224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="5" t="n"/>
+      <c r="I225" s="5" t="n"/>
+      <c r="J225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
+      <c r="J227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
+      <c r="J228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
+      <c r="J232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="5" t="n"/>
+      <c r="I233" s="5" t="n"/>
+      <c r="J233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="5" t="n"/>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
+      <c r="J237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
+      <c r="J238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
+      <c r="J240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
+      <c r="J241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
+      <c r="J242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="5" t="n"/>
+      <c r="I243" s="5" t="n"/>
+      <c r="J243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
+      <c r="J244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
+      <c r="J245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
+      <c r="J246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="5" t="n"/>
+      <c r="I247" s="5" t="n"/>
+      <c r="J247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="5" t="n"/>
+      <c r="I248" s="5" t="n"/>
+      <c r="J248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
+      <c r="J249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+      <c r="J250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
+      <c r="J251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="5" t="n"/>
+      <c r="I252" s="5" t="n"/>
+      <c r="J252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+      <c r="J253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5" t="n"/>
+      <c r="I254" s="5" t="n"/>
+      <c r="J254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="5" t="n"/>
+      <c r="I255" s="5" t="n"/>
+      <c r="J255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
+      <c r="J256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="5" t="n"/>
+      <c r="I257" s="5" t="n"/>
+      <c r="J257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+      <c r="J258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="5" t="n"/>
+      <c r="I259" s="5" t="n"/>
+      <c r="J259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="5" t="n"/>
+      <c r="I261" s="5" t="n"/>
+      <c r="J261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
+      <c r="J262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
+      <c r="J263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="5" t="n"/>
+      <c r="I264" s="5" t="n"/>
+      <c r="J264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
+      <c r="J265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="5" t="n"/>
+      <c r="I266" s="5" t="n"/>
+      <c r="J266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
+      <c r="J267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
+      <c r="J268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
+      <c r="J269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
+      <c r="J270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
+      <c r="J271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
+      <c r="J273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5" t="n"/>
+      <c r="I274" s="5" t="n"/>
+      <c r="J274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
+      <c r="J275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
+      <c r="J276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
+      <c r="J277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+      <c r="J278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="5" t="n"/>
+      <c r="I279" s="5" t="n"/>
+      <c r="J279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="5" t="n"/>
+      <c r="I280" s="5" t="n"/>
+      <c r="J280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
+      <c r="J281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="5" t="n"/>
+      <c r="I282" s="5" t="n"/>
+      <c r="J282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="5" t="n"/>
+      <c r="I283" s="5" t="n"/>
+      <c r="J283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
+      <c r="J284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="5" t="n"/>
+      <c r="I285" s="5" t="n"/>
+      <c r="J285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="5" t="n"/>
+      <c r="I286" s="5" t="n"/>
+      <c r="J286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="5" t="n"/>
+      <c r="I287" s="5" t="n"/>
+      <c r="J287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
+      <c r="J288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="5" t="n"/>
+      <c r="I289" s="5" t="n"/>
+      <c r="J289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
+      <c r="J290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="5" t="n"/>
+      <c r="I291" s="5" t="n"/>
+      <c r="J291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="5" t="n"/>
+      <c r="I292" s="5" t="n"/>
+      <c r="J292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="5" t="n"/>
+      <c r="I293" s="5" t="n"/>
+      <c r="J293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="5" t="n"/>
+      <c r="I294" s="5" t="n"/>
+      <c r="J294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="5" t="n"/>
+      <c r="I295" s="5" t="n"/>
+      <c r="J295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="5" t="n"/>
+      <c r="I296" s="5" t="n"/>
+      <c r="J296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
+      <c r="J297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
+      <c r="J298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="5" t="n"/>
+      <c r="I299" s="5" t="n"/>
+      <c r="J299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
+      <c r="J300" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3096,7 +4907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3180,7 +4991,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Broto Feliz</t>
+          <t>Banana Verde</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -3190,17 +5001,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Árabe vegetariana</t>
+          <t>Vegetariana natural</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Moema / SP</t>
+          <t>Vila Madalena / SP</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Av. Example, 300</t>
+          <t>Rua Harmonia, 278</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -3220,190 +5031,618 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/brotofeliz</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr"/>
+          <t>instagram.com/restbananaverde</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Pioneiro na Vila Madalena; muitas opções veganas</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Pão &amp; Semente</t>
+          <t>Gopala</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Pães artesanais</t>
+          <t>Indiana / Brasileira</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Perdizes / SP</t>
+          <t>Cerqueira César / SP</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Rua Example, 400</t>
+          <t>Rua Dr. Melo Alves, 54</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/gopalarestaurante</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>2ª unidade: Rua Harmonia, 484 - Vila Madalena</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Gopala Vila Madalena</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Indiana / Brasileira</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Rua Harmonia, 484</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/gopalarestaurante</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Gulab Hari</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Rua Antônio Carlos, 288 - Térreo A2</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/gulabhari</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Com opções veganas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Camélia Òdòdó</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Orgânica / Agroecológica</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Rua Girassol, 451b</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/cameliaododo</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Chef Bela Gil; sex e sáb fecha às 23h</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Maha Mantra</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Indiana / Buffet</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Rua Fradique Coutinho, 766</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/mahamantrasp</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Sáb e Dom fecham às 16h; atmosfera zen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Quincho Cozinha</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Vegetariana criativa</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Rua Mourato Coelho, 1447</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/quinchocozinha</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Dom fecha às 17h; coquetelaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Apfel Centro</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Buffet vegetariano</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Viaduto 9 de Julho, 160 - Sobreloja</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/apfelrestaurante</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Buffet por peso; desde 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Apfel Jardins</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Buffet vegetariano</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Rua Cônego Eugênio Leite, 840</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/apfelrestaurante</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Carrito</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mexicana / Orgânica</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Alameda Tietê, 636</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>instagram.com/carritosp</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Próximo à Av. Paulista; brunch ao jantar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Naturetto Interlagos</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Oriental / Brasileira</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Interlagos / SP</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Av. Antônio Barbosa da Silva Sandoval, 38</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Yakissoba, hot roll, tofu empanado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante Vegano Osasco</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Variada</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Centro / Osasco</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Rua Dante Batiston, 99</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Seg a Sáb</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>paosemente.com.br</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Sáb: 12h às 15h</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante Naturista Barueri</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Variada</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Parque Imperial / Barueri</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Rua Duarte da Costa, 80</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom (exceto ter. 11-20h15)</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Dom fecha às 15h15</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="n"/>
@@ -5612,6 +7851,1206 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="n"/>
       <c r="J200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+      <c r="J201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
+      <c r="J202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+      <c r="J203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
+      <c r="J204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+      <c r="J205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
+      <c r="J206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
+      <c r="J207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+      <c r="J208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+      <c r="J209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="5" t="n"/>
+      <c r="J210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
+      <c r="J211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+      <c r="J212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
+      <c r="J213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
+      <c r="J214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="5" t="n"/>
+      <c r="I215" s="5" t="n"/>
+      <c r="J215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="5" t="n"/>
+      <c r="I216" s="5" t="n"/>
+      <c r="J216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
+      <c r="I217" s="5" t="n"/>
+      <c r="J217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="5" t="n"/>
+      <c r="I218" s="5" t="n"/>
+      <c r="J218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
+      <c r="J219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="5" t="n"/>
+      <c r="I220" s="5" t="n"/>
+      <c r="J220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
+      <c r="J221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
+      <c r="J222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="5" t="n"/>
+      <c r="I223" s="5" t="n"/>
+      <c r="J223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="5" t="n"/>
+      <c r="I224" s="5" t="n"/>
+      <c r="J224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="5" t="n"/>
+      <c r="I225" s="5" t="n"/>
+      <c r="J225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
+      <c r="J227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
+      <c r="J228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
+      <c r="J232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="5" t="n"/>
+      <c r="I233" s="5" t="n"/>
+      <c r="J233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="5" t="n"/>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
+      <c r="J237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
+      <c r="J238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
+      <c r="J240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
+      <c r="J241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
+      <c r="J242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="5" t="n"/>
+      <c r="I243" s="5" t="n"/>
+      <c r="J243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
+      <c r="J244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
+      <c r="J245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
+      <c r="J246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="5" t="n"/>
+      <c r="I247" s="5" t="n"/>
+      <c r="J247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="5" t="n"/>
+      <c r="I248" s="5" t="n"/>
+      <c r="J248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
+      <c r="J249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+      <c r="J250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
+      <c r="J251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="5" t="n"/>
+      <c r="I252" s="5" t="n"/>
+      <c r="J252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+      <c r="J253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5" t="n"/>
+      <c r="I254" s="5" t="n"/>
+      <c r="J254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="5" t="n"/>
+      <c r="I255" s="5" t="n"/>
+      <c r="J255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
+      <c r="J256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="5" t="n"/>
+      <c r="I257" s="5" t="n"/>
+      <c r="J257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+      <c r="J258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="5" t="n"/>
+      <c r="I259" s="5" t="n"/>
+      <c r="J259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="5" t="n"/>
+      <c r="I261" s="5" t="n"/>
+      <c r="J261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
+      <c r="J262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
+      <c r="J263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="5" t="n"/>
+      <c r="I264" s="5" t="n"/>
+      <c r="J264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
+      <c r="J265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="5" t="n"/>
+      <c r="I266" s="5" t="n"/>
+      <c r="J266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
+      <c r="J267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
+      <c r="J268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
+      <c r="J269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
+      <c r="J270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
+      <c r="J271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
+      <c r="J273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5" t="n"/>
+      <c r="I274" s="5" t="n"/>
+      <c r="J274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
+      <c r="J275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
+      <c r="J276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
+      <c r="J277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+      <c r="J278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="5" t="n"/>
+      <c r="I279" s="5" t="n"/>
+      <c r="J279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="5" t="n"/>
+      <c r="I280" s="5" t="n"/>
+      <c r="J280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
+      <c r="J281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="5" t="n"/>
+      <c r="I282" s="5" t="n"/>
+      <c r="J282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="5" t="n"/>
+      <c r="I283" s="5" t="n"/>
+      <c r="J283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
+      <c r="J284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="5" t="n"/>
+      <c r="I285" s="5" t="n"/>
+      <c r="J285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="5" t="n"/>
+      <c r="I286" s="5" t="n"/>
+      <c r="J286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="5" t="n"/>
+      <c r="I287" s="5" t="n"/>
+      <c r="J287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
+      <c r="J288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="5" t="n"/>
+      <c r="I289" s="5" t="n"/>
+      <c r="J289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
+      <c r="J290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="5" t="n"/>
+      <c r="I291" s="5" t="n"/>
+      <c r="J291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="5" t="n"/>
+      <c r="I292" s="5" t="n"/>
+      <c r="J292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="5" t="n"/>
+      <c r="I293" s="5" t="n"/>
+      <c r="J293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="5" t="n"/>
+      <c r="I294" s="5" t="n"/>
+      <c r="J294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="5" t="n"/>
+      <c r="I295" s="5" t="n"/>
+      <c r="J295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="5" t="n"/>
+      <c r="I296" s="5" t="n"/>
+      <c r="J296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
+      <c r="J297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
+      <c r="J298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="5" t="n"/>
+      <c r="I299" s="5" t="n"/>
+      <c r="J299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
+      <c r="J300" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5628,7 +9067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5712,7 +9151,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Casa Verde</t>
+          <t>Casa Jaya</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -5722,17 +9161,17 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Hambúrguer / Americana</t>
+          <t>Contemporânea</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Itaim Bibi / SP</t>
+          <t>Centro / SP</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Rua Example, 500</t>
+          <t>Rua Zacarias de Góis, 1201 - Campo Belo</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -5742,7 +9181,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -5752,66 +9191,26 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>instagram.com/casaverde</t>
+          <t>instagram.com/casajaya</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Menu com opções veganas</t>
+          <t>Projeto cultural e sustentável; sáb e dom até 16h</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Pizza da Terra</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Pizzaria</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Pizza</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Santana / SP</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Rua Example, 600</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Qua a Dom</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>pizzadaterra.com.br</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>Massas veganas disponíveis</t>
-        </is>
-      </c>
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="n"/>
@@ -8152,6 +11551,1206 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="n"/>
       <c r="J200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+      <c r="J201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
+      <c r="J202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+      <c r="J203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
+      <c r="J204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+      <c r="J205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
+      <c r="J206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
+      <c r="J207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+      <c r="J208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+      <c r="J209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="5" t="n"/>
+      <c r="J210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
+      <c r="J211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+      <c r="J212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
+      <c r="J213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
+      <c r="J214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="5" t="n"/>
+      <c r="I215" s="5" t="n"/>
+      <c r="J215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="5" t="n"/>
+      <c r="I216" s="5" t="n"/>
+      <c r="J216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
+      <c r="I217" s="5" t="n"/>
+      <c r="J217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="5" t="n"/>
+      <c r="I218" s="5" t="n"/>
+      <c r="J218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
+      <c r="J219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="5" t="n"/>
+      <c r="I220" s="5" t="n"/>
+      <c r="J220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
+      <c r="J221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
+      <c r="J222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="5" t="n"/>
+      <c r="I223" s="5" t="n"/>
+      <c r="J223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="5" t="n"/>
+      <c r="I224" s="5" t="n"/>
+      <c r="J224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="5" t="n"/>
+      <c r="I225" s="5" t="n"/>
+      <c r="J225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
+      <c r="J227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
+      <c r="J228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
+      <c r="J232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="5" t="n"/>
+      <c r="I233" s="5" t="n"/>
+      <c r="J233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="5" t="n"/>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
+      <c r="J237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
+      <c r="J238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
+      <c r="J240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
+      <c r="J241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
+      <c r="J242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="5" t="n"/>
+      <c r="I243" s="5" t="n"/>
+      <c r="J243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
+      <c r="J244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
+      <c r="J245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
+      <c r="J246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="5" t="n"/>
+      <c r="I247" s="5" t="n"/>
+      <c r="J247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="5" t="n"/>
+      <c r="I248" s="5" t="n"/>
+      <c r="J248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
+      <c r="J249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+      <c r="J250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
+      <c r="J251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="5" t="n"/>
+      <c r="I252" s="5" t="n"/>
+      <c r="J252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+      <c r="J253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5" t="n"/>
+      <c r="I254" s="5" t="n"/>
+      <c r="J254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="5" t="n"/>
+      <c r="I255" s="5" t="n"/>
+      <c r="J255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
+      <c r="J256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="5" t="n"/>
+      <c r="I257" s="5" t="n"/>
+      <c r="J257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+      <c r="J258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="5" t="n"/>
+      <c r="I259" s="5" t="n"/>
+      <c r="J259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="5" t="n"/>
+      <c r="I261" s="5" t="n"/>
+      <c r="J261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
+      <c r="J262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
+      <c r="J263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="5" t="n"/>
+      <c r="I264" s="5" t="n"/>
+      <c r="J264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
+      <c r="J265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="5" t="n"/>
+      <c r="I266" s="5" t="n"/>
+      <c r="J266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
+      <c r="J267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
+      <c r="J268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
+      <c r="J269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
+      <c r="J270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
+      <c r="J271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
+      <c r="J273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5" t="n"/>
+      <c r="I274" s="5" t="n"/>
+      <c r="J274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
+      <c r="J275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
+      <c r="J276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
+      <c r="J277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+      <c r="J278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="5" t="n"/>
+      <c r="I279" s="5" t="n"/>
+      <c r="J279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="5" t="n"/>
+      <c r="I280" s="5" t="n"/>
+      <c r="J280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
+      <c r="J281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="5" t="n"/>
+      <c r="I282" s="5" t="n"/>
+      <c r="J282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="5" t="n"/>
+      <c r="I283" s="5" t="n"/>
+      <c r="J283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
+      <c r="J284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="5" t="n"/>
+      <c r="I285" s="5" t="n"/>
+      <c r="J285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="5" t="n"/>
+      <c r="I286" s="5" t="n"/>
+      <c r="J286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="5" t="n"/>
+      <c r="I287" s="5" t="n"/>
+      <c r="J287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
+      <c r="J288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="5" t="n"/>
+      <c r="I289" s="5" t="n"/>
+      <c r="J289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
+      <c r="J290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="5" t="n"/>
+      <c r="I291" s="5" t="n"/>
+      <c r="J291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="5" t="n"/>
+      <c r="I292" s="5" t="n"/>
+      <c r="J292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="5" t="n"/>
+      <c r="I293" s="5" t="n"/>
+      <c r="J293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="5" t="n"/>
+      <c r="I294" s="5" t="n"/>
+      <c r="J294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="5" t="n"/>
+      <c r="I295" s="5" t="n"/>
+      <c r="J295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="5" t="n"/>
+      <c r="I296" s="5" t="n"/>
+      <c r="J296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
+      <c r="J297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
+      <c r="J298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="5" t="n"/>
+      <c r="I299" s="5" t="n"/>
+      <c r="J299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
+      <c r="J300" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/VegSP_lista.xlsx
+++ b/VegSP_lista.xlsx
@@ -1533,244 +1533,1044 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Subte Vegan Food</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Vegana contemporânea</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Av. São João, 281</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>subtevegan.com.br</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante e cafeteria 100% vegana</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>POP Vegan Food</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Buffet vegano</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Rua Fernando de Albuquerque, 144</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/popveganfood</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Buffet popular vegano</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Animal Chef</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Hamburgueria</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Fast food vegano</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Rua Mourato Coelho, 1084</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/animalchef</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Hambúrgueres veganos</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>A Coruja Vegan</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Churrasco vegano</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Vila Romana / SP</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Rua Tito, 25</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/acoruja_vegan</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Especializado em churrasco vegano</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Prime Dog</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Lanchonete</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hot dog vegano</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>República / SP</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Rua Bento Freitas, 136</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/primedogveg</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Cachorros-quentes veganos</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Lar Vegan</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Brasileira / Buffet</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Bela Vista / SP</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Rua Conselheiro Ramalho, 992</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/larvegan</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Self-service vegano</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Loving Hut</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Asiática / Vegana</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Vila Mariana / SP</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Rua França Pinto, 243</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>lovinghutsaopaulo.com.br</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Rede internacional vegana</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Vaca Verde</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Brasileira</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Moema / SP</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Alameda dos Arapanés, 1424</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/vacaverdeveg</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Feijoada vegana aos finais de semana</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Jaca Verde</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Vegana brasileira</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Santa Cecília / SP</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Rua Sabará, 123</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/jacaverde</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Pratos brasileiros veganos</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Purana Vegan</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Natural / Vegana</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Vila Mariana / SP</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Rua Rio Grande, 150</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/puranavegan</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Comida saudável vegana</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Sushimar Vegano</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Japonesa vegana</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Liberdade / SP</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Rua Galvão Bueno, 425</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/sushimarvegano</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Rodízio vegano japonês</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Veggie Raw</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Raw food</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Rua Cônego Eugênio Leite, 1152</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/veggieraw</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Doces e refeições crudívoras</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>The Vegan Burger</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Hamburgueria</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hambúrguer vegano</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Tatuapé / SP</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Rua Serra de Japi, 987</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/theveganburger</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Lanches veganos artesanais</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Astronauta Café</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Cafeteria vegana</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Rua Simão Álvares, 778</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/astronautacafe</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Brunch e doces veganos</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Plant Made</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Padaria vegana</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Moema / SP</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Av. Bem-te-vi, 210</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/plantmade</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Padaria artesanal vegana</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>São Saruê</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Nordestina vegana</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Bela Vista / SP</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Rua Rui Barbosa, 269</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/saosarue</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Culinária nordestina vegana</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>It's Vegan</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Fast food vegano</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Consolação / SP</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Rua Augusta, 1524</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/itsveganbr</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Fast food 100% vegetal</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Pizza Youth</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Pizza vegana</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Rua dos Pinheiros, 220</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/pizzayouth</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Pizzas veganas artesanais</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Veggie Bites</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Lanchonete</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Vegana</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Santana / SP</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Rua Voluntários da Pátria, 1200</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/veggiebites</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Lanches e bowls</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Vegusto</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Buffet vegano</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Rua Xavier de Toledo, 98</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/vegusto</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Almoço executivo vegano</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="n"/>
@@ -5645,124 +6445,524 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Moinho de Pedra</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Natural / Vegetariana</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Chácara Santo Antônio / SP</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Rua Fernandes Moreira, 73</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/moinhodepedra</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Tradicional vegetariano</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Le Manjue</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Contemporânea saudável</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Rua Domingos Fernandes, 608</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>lemanjue.com</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Alta gastronomia vegetariana</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Alcachofra Natural</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Brasileira / Buffet</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Rua da Quitanda, 199</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/alcachofranatural</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Popular no centro</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Lótus Restaurante Vegetariano</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Indiana / Asiática</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Liberdade / SP</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Rua Galvão Bueno, 123</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/lotusvegetariano</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Buffet vegetariano</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Govinda</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Indiana / Vegetariana</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Rua Gomes de Carvalho, 1666</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/govindasp</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Inspiração ayurvédica</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Apfel</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Vegetariana</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>República / SP</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Rua Dom José de Barros, 99</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/apfelrestaurante</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Clássico vegetariano paulistano</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Natural</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Rua Fradique Coutinho, 910</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/biorestaurante</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Muitas opções sem glúten</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Tandoor Veggie</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Moema / SP</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Alameda Jauaperi, 627</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/tandoorveggie</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Curries e naan vegetarianos</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Ponto Orgânico</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Natural / Orgânico</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Perdizes / SP</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Rua Cardoso de Almeida, 1320</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/pontoorganico</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Ingredientes orgânicos</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Rangoli</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Indiana vegetariana</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Rua Artur de Azevedo, 2134</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/rangoli</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Comida indiana tradicional</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="n"/>
@@ -9201,184 +10401,784 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
-      <c r="J5" s="18" t="n"/>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Congolinária</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Africana</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Santa Cecília / SP</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Rua Barão de Tatuí, 275</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>instagram.com/congolinaria</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>Possui pratos vegetarianos e veganos</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Tuju</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Contemporânea brasileira</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Jardim Paulistano / SP</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Rua Frei Galvão, 135</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>tuju.com.br</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Menu degustação vegetal</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Veridiana Pizzaria</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Pizza artesanal</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Higienópolis / SP</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Rua Dona Veridiana, 661</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>veridiana.com.br</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Possui pizzas veganas</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Le Pain Quotidien</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Café / Restaurante</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Padaria artesanal</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Alameda Lorena, 1914</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>lepainquotidien.com/br</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Opções vegetarianas e veganas</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Djapa</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Japonesa</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Moema / SP</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Alameda dos Arapanés, 1681</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>djapa.com.br</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Rodízio com opções veganas</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Greenjoy</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Saudável</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Itaim Bibi / SP</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Rua Joaquim Floriano, 541</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>greenjoy.com.br</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Bowls vegetarianos</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>NOU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Contemporânea</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Rua dos Pinheiros, 274</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/nourestaurante</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Boas opções vegetarianas</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Modern Mamma Osteria</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Italiana</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Rua Manuel Guedes, 160</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>modernmammaosteria.com</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Massas vegetarianas</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Bráz Pizzaria</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Rua Vupabussu, 271</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>brazpizzaria.com.br</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Opções veganas no cardápio</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Futuro Refeitório</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Café / Restaurante</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Brunch</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Rua Cônego Eugênio Leite, 808</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/futurorefeitorio</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Pratos vegetais e brunch</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Maní</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Contemporânea brasileira</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Jardins / SP</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Rua Joaquim Antunes, 210</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>mani.com.br</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Menu com opções vegetarianas</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A Baianeira</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Brasileira</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Barra Funda / SP</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Rua Dona Elisa, 117</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>instagram.com/abaianeira</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Pratos vegetarianos disponíveis</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Coffee Lab</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Cafeteria</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Rua Fradique Coutinho, 1340</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>coffeelab.com.br</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Leites vegetais e opções veganas</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Municipal A Casa do Porco</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Brasileira</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Rua Araújo, 124</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>acasadoporco.com</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Possui menu vegetal</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Z Deli</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Lanchonete</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hambúrguer</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Rua Francisco Leitão, 16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>zdeli.com.br</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Hambúrguer vegetariano disponível</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="n"/>

--- a/VegSP_lista.xlsx
+++ b/VegSP_lista.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/vhmorbistro</t>
+          <t>https://www.instagram.com/vhmorbistro/</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/saladdays.sp</t>
+          <t>https://www.instagram.com/saladdaysvegan/</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/ratorosapizzaria</t>
+          <t>https://www.instagram.com/ratorosa_/</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/popvegano</t>
+          <t>https://popveganfood.com.br/</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -884,22 +884,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Ter a Sáb (pizza sáb 18-21h)</t>
+          <t>Ter a Sex (sáb: 10-16h)</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/heraveggie</t>
+          <t>https://www.instagram.com/heraveggie/</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -949,11 +949,7 @@
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>instagram.com/itsvegan.sp</t>
-        </is>
-      </c>
+      <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Brunch aos domingos; fecha mais tarde sex e sáb (23h30)</t>
@@ -1003,7 +999,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/jaffasp</t>
+          <t>https://www.instagram.com/jaffasp/</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1055,7 +1051,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/pratada.sp</t>
+          <t>https://www.instagram.com/pratada.sp/</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1107,7 +1103,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/congolinaria</t>
+          <t>https://www.instagram.com/congolinaria/</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1159,7 +1155,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/congolinaria</t>
+          <t>https://www.instagram.com/congolinaria/</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1211,7 +1207,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/veganosp</t>
+          <t>https://www.instagram.com/veganosp/</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/boboemporio</t>
+          <t>https://www.instagram.com/boboemporiovegano/</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1315,7 +1311,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/acorujavegana</t>
+          <t>https://www.instagram.com/acorujavegan/</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1367,7 +1363,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/sushimarvegano</t>
+          <t>https://www.instagram.com/sushimarvegano/</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1419,7 +1415,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/casaraw</t>
+          <t>https://www.instagram.com/casaraw/</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/taucozinhaveg</t>
+          <t>https://www.instagram.com/taucozinha/</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1523,7 +1519,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>instagram.com/lovinghutsp</t>
+          <t>https://lovinghutsaopaulo.com.br/</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1533,1044 +1529,940 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Subte Vegan Food</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Vegana contemporânea</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Centro / SP</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Av. São João, 281</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Seg a Sáb</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>subtevegan.com.br</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/subtevegan/</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Restaurante e cafeteria 100% vegana</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>POP Vegan Food</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Buffet vegano</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Consolação / SP</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Rua Fernando de Albuquerque, 144</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/popveganfood</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>https://popveganfood.com.br/</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Buffet popular vegano</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Animal Chef</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Hamburgueria</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Fast food vegano</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Rua Mourato Coelho, 1084</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/animalchef</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/animalchefbr/</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Hambúrgueres veganos</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>A Coruja Vegan</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Churrasco vegano</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Vila Romana / SP</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Rua Tito, 25</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Qua a Dom</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/acoruja_vegan</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acorujavegan/</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Especializado em churrasco vegano</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Prime Dog</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Lanchonete</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Hot dog vegano</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>República / SP</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Rua Bento Freitas, 136</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/primedogveg</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/primedogoficial/</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Cachorros-quentes veganos</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Lar Vegan</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Brasileira / Buffet</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Bela Vista / SP</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Rua Conselheiro Ramalho, 992</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Seg a Sáb</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/larvegan</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/larvegan/</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Self-service vegano</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Loving Hut</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Vaca Verde</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Asiática / Vegana</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Vila Mariana / SP</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Rua França Pinto, 243</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Vila Olímpia / SP</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Rua Alvorada, 457</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vaca.verde/</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Feijoada vegana aos finais de semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Jaca Verde</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Vegana brasileira</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Santa Cecília / SP</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Rua Sabará, 123</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>lovinghutsaopaulo.com.br</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Rede internacional vegana</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Vaca Verde</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Pratos brasileiros veganos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Purana.Co</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Brasileira</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Moema / SP</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Alameda dos Arapanés, 1424</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Natural / Vegana</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Rua Cônego Eugênio Leite, 840</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/purana.co/</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Comida saudável vegana</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Sushimar Vegano</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Japonesa vegana</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Liberdade / SP</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Rua Galvão Bueno, 425</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/vacaverdeveg</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Feijoada vegana aos finais de semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Jaca Verde</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sushimarvegano/</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Rodízio vegano japonês</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Veggie Raw</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Raw food</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Rua Cônego Eugênio Leite, 1152</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Sáb</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Doces e refeições crudívoras</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>The Vegan Burger</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Hamburgueria</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Hambúrguer vegano</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Tatuapé / SP</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Rua Serra de Japi, 987</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Lanches veganos artesanais</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Astronauta Café</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Cafeteria vegana</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Rua Simão Álvares, 778</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Brunch e doces veganos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Plant Made</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Padaria vegana</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Higienópolis / SP</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Praça Vilaboim, 111</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/plantmadesp/</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Padaria artesanal vegana</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>São Saruê</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Vegana brasileira</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Santa Cecília / SP</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Rua Sabará, 123</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Nordestina vegana</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Bela Vista / SP</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Rua Rui Barbosa, 269</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/saosarue/</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Culinária nordestina vegana</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Pizza Youth</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Pizza vegana</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Rua dos Pinheiros, 220</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/jacaverde</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Pratos brasileiros veganos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Purana Vegan</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pizzayouthbr/</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Pizzas veganas artesanais</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Veggie Bites</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Lanchonete</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Vegana</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Santana / SP</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Rua Voluntários da Pátria, 1200</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Lanches e bowls</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Vegusto</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Natural / Vegana</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Vila Mariana / SP</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Rua Rio Grande, 150</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Buffet vegano</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Centro / SP</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Rua Xavier de Toledo, 98</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Sáb</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/puranavegan</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Comida saudável vegana</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Sushimar Vegano</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Japonesa vegana</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Liberdade / SP</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Rua Galvão Bueno, 425</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Ter a Dom</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/sushimarvegano</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Rodízio vegano japonês</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Veggie Raw</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Café</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Raw food</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Pinheiros / SP</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Rua Cônego Eugênio Leite, 1152</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Ter a Sáb</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/veggieraw</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Doces e refeições crudívoras</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>The Vegan Burger</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Hamburgueria</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Hambúrguer vegano</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Tatuapé / SP</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Rua Serra de Japi, 987</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Dom</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/theveganburger</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Lanches veganos artesanais</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Astronauta Café</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Café</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Cafeteria vegana</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Pinheiros / SP</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Rua Simão Álvares, 778</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Ter a Dom</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/astronautacafe</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>Brunch e doces veganos</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Plant Made</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Padaria</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Padaria vegana</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Moema / SP</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Av. Bem-te-vi, 210</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Dom</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/plantmade</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>Padaria artesanal vegana</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>São Saruê</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Nordestina vegana</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Bela Vista / SP</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Rua Rui Barbosa, 269</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Qua a Dom</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/saosarue</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>Culinária nordestina vegana</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>It's Vegan</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Fast food vegano</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Consolação / SP</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Rua Augusta, 1524</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Dom</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/itsveganbr</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Fast food 100% vegetal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Pizza Youth</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Pizzaria</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Pizza vegana</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Pinheiros / SP</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Rua dos Pinheiros, 220</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Ter a Dom</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/pizzayouth</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>Pizzas veganas artesanais</t>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Almoço executivo vegano</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Veggie Bites</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Lanchonete</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Vegana</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Santana / SP</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Rua Voluntários da Pátria, 1200</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Dom</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/veggiebites</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Lanches e bowls</t>
-        </is>
-      </c>
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Vegusto</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Buffet vegano</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Centro / SP</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Rua Xavier de Toledo, 98</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Seg a Sex</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/vegusto</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>Almoço executivo vegano</t>
-        </is>
-      </c>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="n"/>
@@ -5831,7 +5723,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/restbananaverde</t>
+          <t>https://www.instagram.com/restbananaverde/</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -5883,7 +5775,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/gopalarestaurante</t>
+          <t>https://www.instagram.com/gopalarestaurante/</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -5935,7 +5827,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/gopalarestaurante</t>
+          <t>https://www.instagram.com/gopalarestaurante/</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
@@ -5981,11 +5873,7 @@
           <t>Seg a Sáb</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>instagram.com/gulabhari</t>
-        </is>
-      </c>
+      <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Com opções veganas</t>
@@ -6035,7 +5923,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/cameliaododo</t>
+          <t>https://www.instagram.com/cameliaododo/</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -6085,11 +5973,7 @@
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>instagram.com/mahamantrasp</t>
-        </is>
-      </c>
+      <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Sáb e Dom fecham às 16h; atmosfera zen</t>
@@ -6137,11 +6021,7 @@
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>instagram.com/quinchocozinha</t>
-        </is>
-      </c>
+      <c r="I10" s="8" t="inlineStr"/>
       <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Dom fecha às 17h; coquetelaria</t>
@@ -6191,7 +6071,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/apfelrestaurante</t>
+          <t>https://www.instagram.com/apfelrestaurante/</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -6243,7 +6123,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>instagram.com/apfelrestaurante</t>
+          <t>https://www.instagram.com/apfelrestaurante/</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr"/>
@@ -6289,11 +6169,7 @@
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>instagram.com/carritosp</t>
-        </is>
-      </c>
+      <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Próximo à Av. Paulista; brunch ao jantar</t>
@@ -6445,520 +6321,496 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Moinho de Pedra</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Natural / Vegetariana</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Chácara Santo Antônio / SP</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Rua Fernandes Moreira, 73</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/moinhodepedra</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moinhodepedrarestaurante/</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Tradicional vegetariano</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Le Manjue</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Contemporânea saudável</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Jardins / SP</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Rua Domingos Fernandes, 608</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>lemanjue.com</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lemanjueorganique/</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Alta gastronomia vegetariana</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Alcachofra Natural</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Brasileira / Buffet</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Centro / SP</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Rua da Quitanda, 199</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Seg a Sex</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/alcachofranatural</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Popular no centro</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Lótus Restaurante Vegetariano</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Indiana / Asiática</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Liberdade / SP</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Rua Galvão Bueno, 123</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/lotusvegetariano</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lotusrestaurantevegetariano/</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Buffet vegetariano</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Govinda</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Indiana / Vegetariana</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Centro / SP</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Rua Gomes de Carvalho, 1666</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Seg a Sex</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/govindasp</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Inspiração ayurvédica</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Apfel</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Vegetariana</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>República / SP</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Rua Dom José de Barros, 99</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Seg a Sex</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/apfelrestaurante</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apfelrestaurante/</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Clássico vegetariano paulistano</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Bio</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Rua Fradique Coutinho, 910</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/biorestaurante</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Muitas opções sem glúten</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Tandoor Veggie</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Indiana</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Moema / SP</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Alameda Jauaperi, 627</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/tandoorveggie</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Curries e naan vegetarianos</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Ponto Orgânico</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Natural / Orgânico</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Perdizes / SP</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Rua Cardoso de Almeida, 1320</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Seg a Sáb</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/pontoorganico</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Ingredientes orgânicos</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Rangoli</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Indiana vegetariana</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Rua Artur de Azevedo, 2134</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/rangoli</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>Comida indiana tradicional</t>
         </is>
@@ -10389,11 +10241,7 @@
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>instagram.com/casajaya</t>
-        </is>
-      </c>
+      <c r="I4" s="11" t="inlineStr"/>
       <c r="J4" s="11" t="inlineStr">
         <is>
           <t>Projeto cultural e sustentável; sáb e dom até 16h</t>
@@ -10401,780 +10249,772 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Congolinária</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Africana</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Santa Cecília / SP</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Rua Barão de Tatuí, 275</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>Qua a Dom</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>instagram.com/congolinaria</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/congolinaria/</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>Possui pratos vegetarianos e veganos</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Tuju</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Contemporânea brasileira</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Jardim Paulistano / SP</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Rua Frei Galvão, 135</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>Ter a Sáb</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>tuju.com.br</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>https://tuju.com.br/</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>Menu degustação vegetal</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Veridiana Pizzaria</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Pizzaria</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Pizza artesanal</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Higienópolis / SP</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Rua Dona Veridiana, 661</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>veridiana.com.br</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.veridiana.com.br/</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>Possui pizzas veganas</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Le Pain Quotidien</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Café / Restaurante</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Padaria artesanal</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Jardins / SP</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Alameda Lorena, 1914</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>lepainquotidien.com/br</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>https://www.lepainquotidien.com/br/</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>Opções vegetarianas e veganas</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Djapa</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Japonesa</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Moema / SP</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Alameda dos Arapanés, 1681</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>djapa.com.br</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>https://djapa.com.br/</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>Rodízio com opções veganas</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Greenjoy</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Saudável</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Itaim Bibi / SP</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Rua Joaquim Floriano, 541</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>greenjoy.com.br</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>https://www.greenjoy.com.br/</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Bowls vegetarianos</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>NOU</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Contemporânea</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Rua dos Pinheiros, 274</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/nourestaurante</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>Boas opções vegetarianas</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Modern Mamma Osteria</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Italiana</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Jardins / SP</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Rua Manuel Guedes, 160</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>modernmammaosteria.com</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>https://modernmammaosteria.com/</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Massas vegetarianas</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Bráz Pizzaria</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Pizzaria</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Pizza</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Rua Vupabussu, 271</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>brazpizzaria.com.br</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.brazpizzaria.com.br/</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>Opções veganas no cardápio</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Futuro Refeitório</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Café / Restaurante</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Brunch</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Rua Cônego Eugênio Leite, 808</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/futurorefeitorio</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/futurorefeitorio/</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>Pratos vegetais e brunch</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Maní</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Contemporânea brasileira</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Jardins / SP</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Rua Joaquim Antunes, 210</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Ter a Sáb</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>mani.com.br</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>https://mani.com.br/</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>Menu com opções vegetarianas</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>A Baianeira</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Brasileira</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Barra Funda / SP</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Rua Dona Elisa, 117</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/abaianeira</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>Pratos vegetarianos disponíveis</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Coffee Lab</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Café</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Cafeteria</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Vila Madalena / SP</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Rua Fradique Coutinho, 1340</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>coffeelab.com.br</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coffeelabbr/</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>Leites vegetais e opções veganas</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Mercado Municipal A Casa do Porco</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Restaurante</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Brasileira</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Centro / SP</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Rua Araújo, 124</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Ter a Dom</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>acasadoporco.com</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acasadoporco/</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>Possui menu vegetal</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Z Deli</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Lanchonete</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Hambúrguer</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Pinheiros / SP</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Rua Francisco Leitão, 16</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>Seg a Dom</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>zdeli.com.br</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>https://zdeli.com.br/</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>Hambúrguer vegetariano disponível</t>
         </is>

--- a/VegSP_lista.xlsx
+++ b/VegSP_lista.xlsx
@@ -2441,112 +2441,452 @@
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Padoca Vegan</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Pães / Doces</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Vila Madalena / SP</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Rua Harmonia, 1275</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/padocavegan/</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Buffet café da manhã sáb e dom 9h-13h</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Novos Veganos</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Hamburgueria</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Hambúrguer / Fast food</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Rua Fidalga, 73</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/novosveganos/</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2ª unidade: Av. Água Fria, 1753 - Santana</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Urbã Cozinha Vegana</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Contemporânea</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Água Branca / SP</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Rua Dona Germaine Burchard, 421</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Sex</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Menu diário com 2 opções; reservar com antecedência</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Piccoli Cucina</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Italiana</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Itaim Bibi / SP</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Rua Dr. Alceu de Campos Rodrigues, 170</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>100% vegano; massas frescas artesanais</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>GES YU Vegan Food</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira / Buffet</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Vila Clementino / SP</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Rua Dr. Diogo de Faria, 568</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Buffet vegano R$29,90; inclui sobremesa, sucos e café</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Porco Me Importa</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Lanchonete</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Brasileira / Lanches</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Campo Belo / SP</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Rua Dr. Carlos Augusto de Campos, 231</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Ter a Dom</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/porcome_importa/</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Delivery e retirada; street food vegano</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Clarice Café</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Café / Lanches</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Vila Mariana / SP</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Rua Major Maragliano, 387</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Temático Clarice Lispector; seg-sex 8-15h; sáb 8-18h; dom 8-15h</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Anhangá Vegan Food</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Mexicana</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Santo Amaro / SP</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Rua dos Patriotas, 1080</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Tortillas, tacos, burritos; delivery e retirada</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Pizza Youth</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Pizza napolitana</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Água Branca / SP</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Rua Dona Germaine Burchard, 374</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Qua a Dom</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pizzayouthbr/</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Pizzas individuais veganas; forno a lenha</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="n"/>
@@ -6817,28 +7157,96 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>LAR Vegan</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Brasileira / Buffet</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Perdizes / SP</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Rua Clélia, 278</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Dom fecha às 17h30; salgados, buffet, pizza e lasanha</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>O Vegetariano</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Chinesa / Brasileira</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Paraíso / SP</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Buffet por peso; opções veganas identificadas; sopa miso grátis</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="n"/>
@@ -11021,64 +11429,260 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>A Pizza da Mooca</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Pizza napolitana</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Mooca / SP</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Rua da Mooca, 1747</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apizzadamooca/</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Seg fecha às 22h; opções veganas no cardápio; Top 50 Pizza Mundo</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>A Pizza da Mooca Pinheiros</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Pizza napolitana</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Pinheiros / SP</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Rua João Moura, 529</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apizzadamooca/</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Seg fecha às 22h; opções veganas no cardápio</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>A Pizza da Mooca Vila Mariana</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Pizza napolitana</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Vila Mariana / SP</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Rua Áurea, 198</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apizzadamooca/</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Seg fecha às 22h; espaço externo pet friendly</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Pizzaria Trivial</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Pizzaria</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Butantã / SP</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Rua Pirajussara, s/n</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Seg a Dom</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trivialpizzaria/</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>14 opções veganas no cardápio; desde 1988</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Koufu</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Chinesa</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>República / SP</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Av. São Luís, 187 - Galeria Metrópole, Loja 14</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Seg a Sáb</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Metade do cardápio dedicada a veganos; dentro da Galeria Metrópole</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="n"/>

--- a/VegSP_lista.xlsx
+++ b/VegSP_lista.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -201,6 +201,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -580,6 +590,8 @@
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -647,6 +659,16 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="K3" s="19" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -699,6 +721,12 @@
           <t>2 sábados/mês anunciados no Instagram</t>
         </is>
       </c>
+      <c r="K4" s="20" t="n">
+        <v>-23.5441</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>-46.6419</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -751,6 +779,12 @@
           <t>Feijoada aos sábados</t>
         </is>
       </c>
+      <c r="K5" s="20" t="n">
+        <v>-23.5731</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>-46.6413</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -803,6 +837,12 @@
           <t>Fermentação natural; fecha último dom do mês</t>
         </is>
       </c>
+      <c r="K6" s="20" t="n">
+        <v>-23.5431</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>-46.6429</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -855,6 +895,12 @@
           <t>Buffet à vontade no almoço; rodízio de pizza à noite</t>
         </is>
       </c>
+      <c r="K7" s="20" t="n">
+        <v>-23.5539</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>-46.6601</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -907,6 +953,12 @@
           <t>Pizza aos sábados das 18h às 21h</t>
         </is>
       </c>
+      <c r="K8" s="20" t="n">
+        <v>-23.5542</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>-46.6598</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -955,6 +1007,12 @@
           <t>Brunch aos domingos; fecha mais tarde sex e sáb (23h30)</t>
         </is>
       </c>
+      <c r="K9" s="20" t="n">
+        <v>-23.5543</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>-46.6597</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1007,6 +1065,12 @@
           <t>Falafel premiado; almoço 12-14h30 e jantar 18-22h</t>
         </is>
       </c>
+      <c r="K10" s="20" t="n">
+        <v>-23.5389</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>-46.652</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1059,6 +1123,12 @@
           <t>Sáb e Dom: 12h às 15h</t>
         </is>
       </c>
+      <c r="K11" s="20" t="n">
+        <v>-23.5421</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>-46.6491</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1111,6 +1181,12 @@
           <t>Dom fecha às 21h; 2ª unidade: Rua Caquito, 251 - Penha</t>
         </is>
       </c>
+      <c r="K12" s="20" t="n">
+        <v>-23.5447</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>-46.6729</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1163,6 +1239,12 @@
           <t>Dom fecha às 21h</t>
         </is>
       </c>
+      <c r="K13" s="20" t="n">
+        <v>-23.527</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>-46.553</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1215,6 +1297,12 @@
           <t>Sáb e Dom: 11h30 às 16h</t>
         </is>
       </c>
+      <c r="K14" s="20" t="n">
+        <v>-23.5651</v>
+      </c>
+      <c r="L14" s="20" t="n">
+        <v>-46.6593</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1267,6 +1355,12 @@
           <t>Buffet livre seg a sex</t>
         </is>
       </c>
+      <c r="K15" s="20" t="n">
+        <v>-23.5658</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>-46.6627</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1319,6 +1413,12 @@
           <t>Primeira churrascaria vegana de SP; rodízio disponível</t>
         </is>
       </c>
+      <c r="K16" s="20" t="n">
+        <v>-23.5217</v>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>-46.6982</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1371,6 +1471,12 @@
           <t>Almoço ter-sex 12-14h30; jantar ter-sáb 19-22h30; sáb-dom-fer 12-16h</t>
         </is>
       </c>
+      <c r="K17" s="20" t="n">
+        <v>-23.566</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>-46.663</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1423,6 +1529,12 @@
           <t>Jardim charmoso; vinhos naturais; dom fecha às 16h30</t>
         </is>
       </c>
+      <c r="K18" s="20" t="n">
+        <v>-23.5393</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>-46.6697</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1475,6 +1587,12 @@
           <t>Almoço sáb 12-15h e dom 12h30-16h</t>
         </is>
       </c>
+      <c r="K19" s="20" t="n">
+        <v>-23.5538</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>-46.6886</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1527,6 +1645,12 @@
           <t>Rede internacional; cardápio extenso</t>
         </is>
       </c>
+      <c r="K20" s="20" t="n">
+        <v>-23.5882</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <v>-46.6335</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1579,6 +1703,12 @@
           <t>Restaurante e cafeteria 100% vegana</t>
         </is>
       </c>
+      <c r="K21" s="20" t="n">
+        <v>-23.545</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>-46.639</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1631,6 +1761,12 @@
           <t>Buffet popular vegano</t>
         </is>
       </c>
+      <c r="K22" s="20" t="n">
+        <v>-23.5539</v>
+      </c>
+      <c r="L22" s="20" t="n">
+        <v>-46.6601</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1683,6 +1819,12 @@
           <t>Hambúrgueres veganos</t>
         </is>
       </c>
+      <c r="K23" s="20" t="n">
+        <v>-23.5577</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>-46.6862</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1735,6 +1877,12 @@
           <t>Especializado em churrasco vegano</t>
         </is>
       </c>
+      <c r="K24" s="20" t="n">
+        <v>-23.5217</v>
+      </c>
+      <c r="L24" s="20" t="n">
+        <v>-46.6982</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1787,6 +1935,12 @@
           <t>Cachorros-quentes veganos</t>
         </is>
       </c>
+      <c r="K25" s="20" t="n">
+        <v>-23.5395</v>
+      </c>
+      <c r="L25" s="20" t="n">
+        <v>-46.6404</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1839,6 +1993,12 @@
           <t>Self-service vegano</t>
         </is>
       </c>
+      <c r="K26" s="20" t="n">
+        <v>-23.554</v>
+      </c>
+      <c r="L26" s="20" t="n">
+        <v>-46.6524</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1891,6 +2051,12 @@
           <t>Feijoada vegana aos finais de semana</t>
         </is>
       </c>
+      <c r="K27" s="20" t="n">
+        <v>-23.5953</v>
+      </c>
+      <c r="L27" s="20" t="n">
+        <v>-46.685</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1939,6 +2105,12 @@
           <t>Pratos brasileiros veganos</t>
         </is>
       </c>
+      <c r="K28" s="20" t="n">
+        <v>-23.5389</v>
+      </c>
+      <c r="L28" s="20" t="n">
+        <v>-46.652</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1991,6 +2163,12 @@
           <t>Comida saudável vegana</t>
         </is>
       </c>
+      <c r="K29" s="20" t="n">
+        <v>-23.5628</v>
+      </c>
+      <c r="L29" s="20" t="n">
+        <v>-46.6891</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -2043,6 +2221,12 @@
           <t>Rodízio vegano japonês</t>
         </is>
       </c>
+      <c r="K30" s="20" t="n">
+        <v>-23.5593</v>
+      </c>
+      <c r="L30" s="20" t="n">
+        <v>-46.6381</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2091,6 +2275,12 @@
           <t>Doces e refeições crudívoras</t>
         </is>
       </c>
+      <c r="K31" s="20" t="n">
+        <v>-23.5628</v>
+      </c>
+      <c r="L31" s="20" t="n">
+        <v>-46.6891</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -2139,6 +2329,12 @@
           <t>Lanches veganos artesanais</t>
         </is>
       </c>
+      <c r="K32" s="20" t="n">
+        <v>-23.5363</v>
+      </c>
+      <c r="L32" s="20" t="n">
+        <v>-46.5693</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2187,6 +2383,12 @@
           <t>Brunch e doces veganos</t>
         </is>
       </c>
+      <c r="K33" s="20" t="n">
+        <v>-23.5631</v>
+      </c>
+      <c r="L33" s="20" t="n">
+        <v>-46.6878</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2239,6 +2441,12 @@
           <t>Padaria artesanal vegana</t>
         </is>
       </c>
+      <c r="K34" s="20" t="n">
+        <v>-23.5444</v>
+      </c>
+      <c r="L34" s="20" t="n">
+        <v>-46.6581</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2291,6 +2499,12 @@
           <t>Culinária nordestina vegana</t>
         </is>
       </c>
+      <c r="K35" s="20" t="n">
+        <v>-23.5541</v>
+      </c>
+      <c r="L35" s="20" t="n">
+        <v>-46.6524</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2343,6 +2557,12 @@
           <t>Pizzas veganas artesanais</t>
         </is>
       </c>
+      <c r="K36" s="20" t="n">
+        <v>-23.5196</v>
+      </c>
+      <c r="L36" s="20" t="n">
+        <v>-46.7065</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2391,6 +2611,12 @@
           <t>Lanches e bowls</t>
         </is>
       </c>
+      <c r="K37" s="20" t="n">
+        <v>-23.5045</v>
+      </c>
+      <c r="L37" s="20" t="n">
+        <v>-46.629</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2439,6 +2665,12 @@
           <t>Almoço executivo vegano</t>
         </is>
       </c>
+      <c r="K38" s="20" t="n">
+        <v>-23.546</v>
+      </c>
+      <c r="L38" s="20" t="n">
+        <v>-46.6405</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2491,6 +2723,12 @@
           <t>Buffet café da manhã sáb e dom 9h-13h</t>
         </is>
       </c>
+      <c r="K39" s="20" t="n">
+        <v>-23.552</v>
+      </c>
+      <c r="L39" s="20" t="n">
+        <v>-46.6889</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2543,6 +2781,12 @@
           <t>2ª unidade: Av. Água Fria, 1753 - Santana</t>
         </is>
       </c>
+      <c r="K40" s="20" t="n">
+        <v>-23.5612</v>
+      </c>
+      <c r="L40" s="20" t="n">
+        <v>-46.6876</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2591,6 +2835,12 @@
           <t>Menu diário com 2 opções; reservar com antecedência</t>
         </is>
       </c>
+      <c r="K41" s="20" t="n">
+        <v>-23.5229</v>
+      </c>
+      <c r="L41" s="20" t="n">
+        <v>-46.7075</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2639,6 +2889,12 @@
           <t>100% vegano; massas frescas artesanais</t>
         </is>
       </c>
+      <c r="K42" s="20" t="n">
+        <v>-23.5848</v>
+      </c>
+      <c r="L42" s="20" t="n">
+        <v>-46.6773</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2687,6 +2943,12 @@
           <t>Buffet vegano R$29,90; inclui sobremesa, sucos e café</t>
         </is>
       </c>
+      <c r="K43" s="20" t="n">
+        <v>-23.5994</v>
+      </c>
+      <c r="L43" s="20" t="n">
+        <v>-46.6425</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2739,6 +3001,12 @@
           <t>Delivery e retirada; street food vegano</t>
         </is>
       </c>
+      <c r="K44" s="20" t="n">
+        <v>-23.6193</v>
+      </c>
+      <c r="L44" s="20" t="n">
+        <v>-46.6965</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -2787,6 +3055,12 @@
           <t>Temático Clarice Lispector; seg-sex 8-15h; sáb 8-18h; dom 8-15h</t>
         </is>
       </c>
+      <c r="K45" s="20" t="n">
+        <v>-23.5882</v>
+      </c>
+      <c r="L45" s="20" t="n">
+        <v>-46.6335</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -2835,6 +3109,12 @@
           <t>Tortillas, tacos, burritos; delivery e retirada</t>
         </is>
       </c>
+      <c r="K46" s="20" t="n">
+        <v>-23.643</v>
+      </c>
+      <c r="L46" s="20" t="n">
+        <v>-46.696</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -2886,6 +3166,12 @@
         <is>
           <t>Pizzas individuais veganas; forno a lenha</t>
         </is>
+      </c>
+      <c r="K47" s="20" t="n">
+        <v>-23.5196</v>
+      </c>
+      <c r="L47" s="20" t="n">
+        <v>-46.7065</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -5939,7 +6225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5952,6 +6238,8 @@
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6019,6 +6307,16 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -6071,6 +6369,12 @@
           <t>Pioneiro na Vila Madalena; muitas opções veganas</t>
         </is>
       </c>
+      <c r="K4" s="20" t="n">
+        <v>-23.5565</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>-46.6868</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -6123,6 +6427,12 @@
           <t>2ª unidade: Rua Harmonia, 484 - Vila Madalena</t>
         </is>
       </c>
+      <c r="K5" s="20" t="n">
+        <v>-23.563</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>-46.668</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -6171,6 +6481,12 @@
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="20" t="n">
+        <v>-23.557</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>-46.6875</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -6219,6 +6535,12 @@
           <t>Com opções veganas</t>
         </is>
       </c>
+      <c r="K7" s="20" t="n">
+        <v>-23.5558</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>-46.6601</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -6271,6 +6593,12 @@
           <t>Chef Bela Gil; sex e sáb fecha às 23h</t>
         </is>
       </c>
+      <c r="K8" s="20" t="n">
+        <v>-23.5548</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>-46.6872</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -6319,6 +6647,12 @@
           <t>Sáb e Dom fecham às 16h; atmosfera zen</t>
         </is>
       </c>
+      <c r="K9" s="20" t="n">
+        <v>-23.556</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>-46.688</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -6367,6 +6701,12 @@
           <t>Dom fecha às 17h; coquetelaria</t>
         </is>
       </c>
+      <c r="K10" s="20" t="n">
+        <v>-23.557</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>-46.684</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -6419,6 +6759,12 @@
           <t>Buffet por peso; desde 2002</t>
         </is>
       </c>
+      <c r="K11" s="20" t="n">
+        <v>-23.545</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>-46.639</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -6467,6 +6813,12 @@
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="20" t="n">
+        <v>-23.5628</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>-46.6891</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -6515,6 +6867,12 @@
           <t>Próximo à Av. Paulista; brunch ao jantar</t>
         </is>
       </c>
+      <c r="K13" s="20" t="n">
+        <v>-23.5669</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>-46.6601</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -6563,6 +6921,12 @@
           <t>Yakissoba, hot roll, tofu empanado</t>
         </is>
       </c>
+      <c r="K14" s="20" t="n">
+        <v>-23.7093</v>
+      </c>
+      <c r="L14" s="20" t="n">
+        <v>-46.6967</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -6611,6 +6975,12 @@
           <t>Sáb: 12h às 15h</t>
         </is>
       </c>
+      <c r="K15" s="20" t="n">
+        <v>-23.5323</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>-46.7912</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -6659,6 +7029,12 @@
           <t>Dom fecha às 15h15</t>
         </is>
       </c>
+      <c r="K16" s="20" t="n">
+        <v>-23.505</v>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>-46.8764</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -6711,6 +7087,12 @@
           <t>Tradicional vegetariano</t>
         </is>
       </c>
+      <c r="K17" s="20" t="n">
+        <v>-23.624</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>-46.698</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -6763,6 +7145,12 @@
           <t>Alta gastronomia vegetariana</t>
         </is>
       </c>
+      <c r="K18" s="20" t="n">
+        <v>-23.5919</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>-46.6624</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -6811,6 +7199,12 @@
           <t>Popular no centro</t>
         </is>
       </c>
+      <c r="K19" s="20" t="n">
+        <v>-23.543</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>-46.634</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -6863,6 +7257,12 @@
           <t>Buffet vegetariano</t>
         </is>
       </c>
+      <c r="K20" s="20" t="n">
+        <v>-23.5593</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <v>-46.6381</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -6911,6 +7311,12 @@
           <t>Inspiração ayurvédica</t>
         </is>
       </c>
+      <c r="K21" s="20" t="n">
+        <v>-23.598</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>-46.691</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -6963,6 +7369,12 @@
           <t>Clássico vegetariano paulistano</t>
         </is>
       </c>
+      <c r="K22" s="20" t="n">
+        <v>-23.544</v>
+      </c>
+      <c r="L22" s="20" t="n">
+        <v>-46.6382</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -7011,6 +7423,12 @@
           <t>Muitas opções sem glúten</t>
         </is>
       </c>
+      <c r="K23" s="20" t="n">
+        <v>-23.5565</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>-46.6876</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -7059,6 +7477,12 @@
           <t>Curries e naan vegetarianos</t>
         </is>
       </c>
+      <c r="K24" s="20" t="n">
+        <v>-23.6046</v>
+      </c>
+      <c r="L24" s="20" t="n">
+        <v>-46.664</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
@@ -7107,6 +7531,12 @@
           <t>Ingredientes orgânicos</t>
         </is>
       </c>
+      <c r="K25" s="20" t="n">
+        <v>-23.5393</v>
+      </c>
+      <c r="L25" s="20" t="n">
+        <v>-46.6697</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -7155,6 +7585,12 @@
           <t>Comida indiana tradicional</t>
         </is>
       </c>
+      <c r="K26" s="20" t="n">
+        <v>-23.562</v>
+      </c>
+      <c r="L26" s="20" t="n">
+        <v>-46.686</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -7203,6 +7639,12 @@
           <t>Dom fecha às 17h30; salgados, buffet, pizza e lasanha</t>
         </is>
       </c>
+      <c r="K27" s="20" t="n">
+        <v>-23.5393</v>
+      </c>
+      <c r="L27" s="20" t="n">
+        <v>-46.6697</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -7246,6 +7688,12 @@
         <is>
           <t>Buffet por peso; opções veganas identificadas; sopa miso grátis</t>
         </is>
+      </c>
+      <c r="K28" s="20" t="n">
+        <v>-23.573</v>
+      </c>
+      <c r="L28" s="20" t="n">
+        <v>-46.642</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -10527,7 +10975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -10540,6 +10988,8 @@
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -10607,6 +11057,16 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -10655,6 +11115,12 @@
           <t>Projeto cultural e sustentável; sáb e dom até 16h</t>
         </is>
       </c>
+      <c r="K4" s="20" t="n">
+        <v>-23.623</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>-46.678</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -10707,6 +11173,12 @@
           <t>Possui pratos vegetarianos e veganos</t>
         </is>
       </c>
+      <c r="K5" s="20" t="n">
+        <v>-23.5447</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>-46.6729</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -10759,6 +11231,12 @@
           <t>Menu degustação vegetal</t>
         </is>
       </c>
+      <c r="K6" s="20" t="n">
+        <v>-23.5697</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>-46.68</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -10811,6 +11289,12 @@
           <t>Possui pizzas veganas</t>
         </is>
       </c>
+      <c r="K7" s="20" t="n">
+        <v>-23.5485</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>-46.6588</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -10863,6 +11347,12 @@
           <t>Opções vegetarianas e veganas</t>
         </is>
       </c>
+      <c r="K8" s="20" t="n">
+        <v>-23.568</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>-46.665</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -10915,6 +11405,12 @@
           <t>Rodízio com opções veganas</t>
         </is>
       </c>
+      <c r="K9" s="20" t="n">
+        <v>-23.6034</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>-46.668</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -10967,6 +11463,12 @@
           <t>Bowls vegetarianos</t>
         </is>
       </c>
+      <c r="K10" s="20" t="n">
+        <v>-23.5848</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>-46.6773</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -11015,6 +11517,12 @@
           <t>Boas opções vegetarianas</t>
         </is>
       </c>
+      <c r="K11" s="20" t="n">
+        <v>-23.5612</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>-46.6876</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -11067,6 +11575,12 @@
           <t>Massas vegetarianas</t>
         </is>
       </c>
+      <c r="K12" s="20" t="n">
+        <v>-23.5866</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>-46.6743</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -11119,6 +11633,12 @@
           <t>Opções veganas no cardápio</t>
         </is>
       </c>
+      <c r="K13" s="20" t="n">
+        <v>-23.5594</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>-46.6902</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -11171,6 +11691,12 @@
           <t>Pratos vegetais e brunch</t>
         </is>
       </c>
+      <c r="K14" s="20" t="n">
+        <v>-23.5628</v>
+      </c>
+      <c r="L14" s="20" t="n">
+        <v>-46.6891</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -11223,6 +11749,12 @@
           <t>Menu com opções vegetarianas</t>
         </is>
       </c>
+      <c r="K15" s="20" t="n">
+        <v>-23.563</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>-46.68</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -11271,6 +11803,12 @@
           <t>Pratos vegetarianos disponíveis</t>
         </is>
       </c>
+      <c r="K16" s="20" t="n">
+        <v>-23.5246</v>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>-46.6703</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -11323,6 +11861,12 @@
           <t>Leites vegetais e opções veganas</t>
         </is>
       </c>
+      <c r="K17" s="20" t="n">
+        <v>-23.556</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>-46.688</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -11375,6 +11919,12 @@
           <t>Possui menu vegetal</t>
         </is>
       </c>
+      <c r="K18" s="20" t="n">
+        <v>-23.5417</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>-46.6343</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -11427,6 +11977,12 @@
           <t>Hambúrguer vegetariano disponível</t>
         </is>
       </c>
+      <c r="K19" s="20" t="n">
+        <v>-23.5627</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>-46.6899</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -11479,6 +12035,12 @@
           <t>Seg fecha às 22h; opções veganas no cardápio; Top 50 Pizza Mundo</t>
         </is>
       </c>
+      <c r="K20" s="20" t="n">
+        <v>-23.5432</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <v>-46.5989</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -11531,6 +12093,12 @@
           <t>Seg fecha às 22h; opções veganas no cardápio</t>
         </is>
       </c>
+      <c r="K21" s="20" t="n">
+        <v>-23.5594</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>-46.6857</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -11583,6 +12151,12 @@
           <t>Seg fecha às 22h; espaço externo pet friendly</t>
         </is>
       </c>
+      <c r="K22" s="20" t="n">
+        <v>-23.591</v>
+      </c>
+      <c r="L22" s="20" t="n">
+        <v>-46.6285</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -11635,6 +12209,12 @@
           <t>14 opções veganas no cardápio; desde 1988</t>
         </is>
       </c>
+      <c r="K23" s="20" t="n">
+        <v>-23.5892</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>-46.7335</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -11682,6 +12262,12 @@
         <is>
           <t>Metade do cardápio dedicada a veganos; dentro da Galeria Metrópole</t>
         </is>
+      </c>
+      <c r="K24" s="20" t="n">
+        <v>-23.5441</v>
+      </c>
+      <c r="L24" s="20" t="n">
+        <v>-46.6419</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
